--- a/src/online_annotation_revised_2024_glycan_zf_OG_brain_20240817temp.xlsx
+++ b/src/online_annotation_revised_2024_glycan_zf_OG_brain_20240817temp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sakazuki\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\其他電腦\My Computer\GlycoMSParser\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B16A2626-34C7-4441-B235-D6443C89A28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F33437-0562-465A-AD99-196E9F9FA9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="1110" windowWidth="18450" windowHeight="13515" activeTab="4" xr2:uid="{4DD463D7-373D-47F4-A03B-74B0493A6743}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{4DD463D7-373D-47F4-A03B-74B0493A6743}"/>
   </bookViews>
   <sheets>
     <sheet name="Glycanlist" sheetId="1" r:id="rId1"/>
@@ -508,10 +508,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">peak </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>charge</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -915,6 +911,10 @@
   </si>
   <si>
     <t>Hex1HexNAc1dHex1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>peak</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -922,7 +922,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1022,10 +1022,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1346,7 +1342,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDF71EC-E688-4FB5-A472-C08A93821269}">
   <dimension ref="A1:Q57"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
     <col min="2" max="2" width="24.125" customWidth="1"/>
@@ -1358,7 +1354,7 @@
     <col min="15" max="15" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1399,7 +1395,7 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O1" t="s">
         <v>13</v>
@@ -1408,7 +1404,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17">
       <c r="B2" t="s">
         <v>74</v>
       </c>
@@ -1441,7 +1437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17">
       <c r="B3" t="s">
         <v>90</v>
       </c>
@@ -1474,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17">
       <c r="B4" t="s">
         <v>92</v>
       </c>
@@ -1504,7 +1500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17">
       <c r="B5" t="s">
         <v>93</v>
       </c>
@@ -1534,7 +1530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17">
       <c r="B6" t="s">
         <v>95</v>
       </c>
@@ -1567,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17">
       <c r="B7" t="s">
         <v>94</v>
       </c>
@@ -1597,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1633,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1672,13 +1668,13 @@
         <v>6</v>
       </c>
       <c r="P9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1714,10 +1710,10 @@
         <v>5</v>
       </c>
       <c r="P10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1753,13 +1749,13 @@
         <v>3</v>
       </c>
       <c r="P11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1795,13 +1791,13 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>6</v>
       </c>
@@ -1837,7 +1833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>7</v>
       </c>
@@ -1873,13 +1869,13 @@
         <v>6</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>8</v>
       </c>
@@ -1915,7 +1911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17">
       <c r="C16" t="s">
         <v>97</v>
       </c>
@@ -1945,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16">
       <c r="C17" t="s">
         <v>98</v>
       </c>
@@ -1978,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16">
       <c r="C18" t="s">
         <v>99</v>
       </c>
@@ -2011,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="C19" t="s">
         <v>100</v>
       </c>
@@ -2047,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>9</v>
       </c>
@@ -2086,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16">
       <c r="C21" t="s">
         <v>101</v>
       </c>
@@ -2119,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>10</v>
       </c>
@@ -2158,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>11</v>
       </c>
@@ -2197,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="C24" t="s">
         <v>102</v>
       </c>
@@ -2233,7 +2229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16">
       <c r="C25" t="s">
         <v>103</v>
       </c>
@@ -2266,7 +2262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16">
       <c r="B26" t="s">
         <v>105</v>
       </c>
@@ -2302,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>12</v>
       </c>
@@ -2341,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>13</v>
       </c>
@@ -2383,7 +2379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16">
       <c r="C29" t="s">
         <v>106</v>
       </c>
@@ -2416,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>14</v>
       </c>
@@ -2458,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>15</v>
       </c>
@@ -2500,10 +2496,10 @@
         <v>4</v>
       </c>
       <c r="P31" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="C32" t="s">
         <v>107</v>
       </c>
@@ -2536,10 +2532,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>16</v>
       </c>
@@ -2578,10 +2574,10 @@
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>17</v>
       </c>
@@ -2620,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>18</v>
       </c>
@@ -2659,7 +2655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>19</v>
       </c>
@@ -2698,7 +2694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>20</v>
       </c>
@@ -2737,7 +2733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>21</v>
       </c>
@@ -2776,10 +2772,10 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>22</v>
       </c>
@@ -2818,7 +2814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16">
       <c r="B40" t="s">
         <v>109</v>
       </c>
@@ -2854,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>23</v>
       </c>
@@ -2893,7 +2889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>24</v>
       </c>
@@ -2932,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>25</v>
       </c>
@@ -2971,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>26</v>
       </c>
@@ -3010,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>28</v>
       </c>
@@ -3049,7 +3045,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>27</v>
       </c>
@@ -3088,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>29</v>
       </c>
@@ -3130,9 +3126,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16">
       <c r="C48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D48">
         <f t="shared" si="4"/>
@@ -3163,10 +3159,10 @@
         <v>2</v>
       </c>
       <c r="P48" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>30</v>
       </c>
@@ -3205,7 +3201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>31</v>
       </c>
@@ -3244,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="P50" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>32</v>
       </c>
@@ -3286,7 +3282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16">
       <c r="B52" t="s">
         <v>108</v>
       </c>
@@ -3322,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16">
       <c r="A53">
         <v>33</v>
       </c>
@@ -3364,7 +3360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16">
       <c r="B54" t="s">
         <v>109</v>
       </c>
@@ -3397,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16">
       <c r="C55" t="s">
         <v>111</v>
       </c>
@@ -3430,12 +3426,12 @@
         <v>0</v>
       </c>
       <c r="P55" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="C56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D56">
         <f t="shared" si="4"/>
@@ -3466,9 +3462,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16">
       <c r="C57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D57">
         <f t="shared" si="4"/>
@@ -3513,45 +3509,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE32C3E9-80B5-4AD0-BB87-D8B256A59B2E}">
   <dimension ref="A1:J115"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
     <col min="8" max="8" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>114</v>
       </c>
       <c r="B1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1" t="s">
         <v>190</v>
       </c>
-      <c r="C1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>191</v>
-      </c>
-      <c r="I1" t="s">
-        <v>192</v>
       </c>
       <c r="J1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -3571,7 +3567,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -3591,7 +3587,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -3611,9 +3607,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5">
         <v>6657</v>
@@ -3634,9 +3630,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B6">
         <v>6741</v>
@@ -3654,9 +3650,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B7">
         <v>6819</v>
@@ -3674,9 +3670,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8">
         <v>6913</v>
@@ -3694,7 +3690,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3714,7 +3710,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -3737,7 +3733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -3760,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -3783,7 +3779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -3806,7 +3802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -3829,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -3852,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3875,7 +3871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -3898,7 +3894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3921,7 +3917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -3944,7 +3940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -3967,7 +3963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -3990,7 +3986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4013,9 +4009,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B23">
         <v>8610</v>
@@ -4036,9 +4032,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B24">
         <v>8707</v>
@@ -4059,9 +4055,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B25">
         <v>8796</v>
@@ -4082,9 +4078,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B26">
         <v>8881</v>
@@ -4105,7 +4101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4128,9 +4124,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B28">
         <v>10067</v>
@@ -4151,9 +4147,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B29">
         <v>10163</v>
@@ -4174,7 +4170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -4194,7 +4190,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -4214,7 +4210,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -4234,7 +4230,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -4254,7 +4250,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>30</v>
       </c>
@@ -4274,7 +4270,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -4294,7 +4290,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -4314,7 +4310,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -4334,7 +4330,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -4354,7 +4350,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -4374,7 +4370,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>31</v>
       </c>
@@ -4394,7 +4390,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -4411,10 +4407,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -4431,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -4451,10 +4447,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -4471,10 +4467,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -4491,10 +4487,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -4511,10 +4507,10 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -4531,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>43</v>
       </c>
@@ -4551,10 +4547,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>43</v>
       </c>
@@ -4571,10 +4567,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
         <v>43</v>
       </c>
@@ -4591,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
         <v>43</v>
       </c>
@@ -4611,16 +4607,16 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
+        <v>155</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
         <v>156</v>
       </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-      <c r="H51" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
         <v>43</v>
       </c>
@@ -4637,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
         <v>43</v>
       </c>
@@ -4660,13 +4656,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -4683,13 +4679,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
         <v>43</v>
       </c>
@@ -4706,13 +4702,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>43</v>
       </c>
@@ -4732,7 +4728,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>43</v>
       </c>
@@ -4752,7 +4748,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>43</v>
       </c>
@@ -4772,7 +4768,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
         <v>43</v>
       </c>
@@ -4792,7 +4788,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>43</v>
       </c>
@@ -4809,10 +4805,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>43</v>
       </c>
@@ -4829,10 +4825,10 @@
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>43</v>
       </c>
@@ -4849,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
         <v>43</v>
       </c>
@@ -4869,10 +4865,10 @@
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>45</v>
       </c>
@@ -4889,10 +4885,10 @@
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>45</v>
       </c>
@@ -4909,10 +4905,10 @@
         <v>0</v>
       </c>
       <c r="F65" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>45</v>
       </c>
@@ -4929,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>45</v>
       </c>
@@ -4949,10 +4945,10 @@
         <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>45</v>
       </c>
@@ -4969,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>45</v>
       </c>
@@ -4989,10 +4985,10 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>45</v>
       </c>
@@ -5009,10 +5005,10 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>45</v>
       </c>
@@ -5029,10 +5025,10 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>45</v>
       </c>
@@ -5049,10 +5045,10 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>45</v>
       </c>
@@ -5069,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>45</v>
       </c>
@@ -5089,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>45</v>
       </c>
@@ -5109,10 +5105,10 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>45</v>
       </c>
@@ -5129,10 +5125,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>45</v>
       </c>
@@ -5149,10 +5145,10 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>45</v>
       </c>
@@ -5169,10 +5165,10 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>45</v>
       </c>
@@ -5189,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>45</v>
       </c>
@@ -5209,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>45</v>
       </c>
@@ -5229,10 +5225,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>47</v>
       </c>
@@ -5252,7 +5248,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>47</v>
       </c>
@@ -5269,10 +5265,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>47</v>
       </c>
@@ -5289,10 +5285,10 @@
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>47</v>
       </c>
@@ -5309,10 +5305,10 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>49</v>
       </c>
@@ -5329,10 +5325,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>49</v>
       </c>
@@ -5349,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>51</v>
       </c>
@@ -5369,10 +5365,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>51</v>
       </c>
@@ -5389,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>51</v>
       </c>
@@ -5409,10 +5405,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>51</v>
       </c>
@@ -5429,10 +5425,10 @@
         <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>51</v>
       </c>
@@ -5449,10 +5445,10 @@
         <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>51</v>
       </c>
@@ -5469,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>51</v>
       </c>
@@ -5489,10 +5485,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>53</v>
       </c>
@@ -5509,10 +5505,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>63</v>
       </c>
@@ -5529,10 +5525,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>63</v>
       </c>
@@ -5549,10 +5545,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>63</v>
       </c>
@@ -5569,10 +5565,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>63</v>
       </c>
@@ -5589,10 +5585,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>63</v>
       </c>
@@ -5609,10 +5605,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>63</v>
       </c>
@@ -5629,10 +5625,10 @@
         <v>0</v>
       </c>
       <c r="F101" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>63</v>
       </c>
@@ -5649,10 +5645,10 @@
         <v>0</v>
       </c>
       <c r="F102" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>63</v>
       </c>
@@ -5669,10 +5665,10 @@
         <v>0</v>
       </c>
       <c r="F103" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>63</v>
       </c>
@@ -5689,10 +5685,10 @@
         <v>0</v>
       </c>
       <c r="F104" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>65</v>
       </c>
@@ -5709,10 +5705,10 @@
         <v>0</v>
       </c>
       <c r="F105" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>65</v>
       </c>
@@ -5729,10 +5725,10 @@
         <v>0</v>
       </c>
       <c r="F106" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>65</v>
       </c>
@@ -5749,12 +5745,12 @@
         <v>0</v>
       </c>
       <c r="F107" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B108">
         <v>14759</v>
@@ -5769,12 +5765,12 @@
         <v>0</v>
       </c>
       <c r="F108" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B109">
         <v>14846</v>
@@ -5789,10 +5785,10 @@
         <v>0</v>
       </c>
       <c r="F109" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>68</v>
       </c>
@@ -5809,10 +5805,10 @@
         <v>0</v>
       </c>
       <c r="F110" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>68</v>
       </c>
@@ -5829,10 +5825,10 @@
         <v>0</v>
       </c>
       <c r="F111" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>73</v>
       </c>
@@ -5849,10 +5845,10 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>73</v>
       </c>
@@ -5869,10 +5865,10 @@
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>73</v>
       </c>
@@ -5889,10 +5885,10 @@
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>73</v>
       </c>
@@ -5909,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -5922,7 +5918,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334E11EA-2936-43B0-A0E7-BCD1C3337C41}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5932,13 +5928,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC3FE90-09BA-46FC-B714-59903BDD25AC}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="47.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -5946,7 +5942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -5954,7 +5950,7 @@
         <v>45491</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5962,7 +5958,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -5970,29 +5966,29 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="66">
       <c r="B11" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="B14" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -6007,7 +6003,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C36264D-C27F-4AD5-963C-3034536B9C46}">
   <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="13.625" customWidth="1"/>
@@ -6016,174 +6012,174 @@
     <col min="5" max="5" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" t="s">
         <v>118</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>119</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>121</v>
       </c>
-      <c r="E1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>122</v>
-      </c>
-      <c r="B2" t="s">
-        <v>123</v>
       </c>
       <c r="C2">
         <v>187.09649999999999</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C3">
         <v>209.12270000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4">
         <v>228.12299999999999</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="C5">
         <v>246.1336</v>
       </c>
       <c r="D5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>260.14920000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7">
         <v>262.16489999999999</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8">
         <v>264.14420000000001</v>
       </c>
       <c r="D8" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9">
         <v>276.18049999999999</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="B10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C10">
         <v>278.15980000000002</v>
       </c>
       <c r="D10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11">
         <v>280.1755</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12">
         <v>294.19110000000001</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="C13">
         <v>303.1438</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="C14">
         <v>335.17</v>
       </c>
@@ -6192,25 +6188,25 @@
         <v>32.026200000000017</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15">
         <v>344.17039999999997</v>
       </c>
       <c r="D15" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="C16">
         <v>374.18099999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17">
         <v>376.19659999999999</v>
@@ -6220,7 +6216,7 @@
         <v>2.0156000000000063</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="C18">
         <v>406.2072</v>
       </c>
@@ -6229,372 +6225,372 @@
         <v>30.010600000000011</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" t="s">
         <v>194</v>
-      </c>
-      <c r="B19" t="s">
-        <v>195</v>
       </c>
       <c r="C19">
         <v>420.22280000000001</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="C20">
         <v>432.22280000000001</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="B21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21">
         <v>434.23849999999999</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C22">
         <v>450.23340000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23">
         <v>464.24900000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="C24">
         <v>482.25959999999998</v>
       </c>
       <c r="D24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="B25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25">
         <v>484.27519999999998</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="B26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C26">
         <v>491.25990000000002</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="C27">
         <v>498.29090000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="B28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C28">
         <v>505.2756</v>
       </c>
       <c r="D28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E28" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="C29">
         <v>525.30179999999996</v>
       </c>
       <c r="D29" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" t="s">
         <v>174</v>
       </c>
-      <c r="E29" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:5">
       <c r="B30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30">
         <v>539.26980000000003</v>
       </c>
       <c r="D30" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="C31">
         <v>539.31740000000002</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E31" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="B32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C32">
         <v>566.28070000000002</v>
       </c>
       <c r="D32" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="B33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33">
         <v>580.29639999999995</v>
       </c>
       <c r="D33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="B34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C34">
         <v>596.29129999999998</v>
       </c>
       <c r="D34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="B35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C35">
         <v>610.30690000000004</v>
       </c>
       <c r="D35" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="B36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C36">
         <v>614.33820000000003</v>
       </c>
       <c r="D36" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="B37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C37">
         <v>624.32259999999997</v>
       </c>
       <c r="D37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38">
         <v>638.33820000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="B39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C39">
         <v>655.31719999999996</v>
       </c>
       <c r="D39" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="C40">
         <v>655.36479999999995</v>
       </c>
       <c r="D40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="B41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C41">
         <v>668.34879999999998</v>
       </c>
       <c r="D41" t="s">
+        <v>210</v>
+      </c>
+      <c r="E41" t="s">
         <v>211</v>
       </c>
-      <c r="E41" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:5">
       <c r="B42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C42">
         <v>679.36479999999995</v>
       </c>
       <c r="D42" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="C43">
         <v>685.37530000000004</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="B44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C44">
         <v>737.37030000000004</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="C45">
         <v>743.41719999999998</v>
       </c>
       <c r="D45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="B46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C46">
         <v>767.38080000000002</v>
       </c>
       <c r="D46" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="B47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47">
         <v>797.39139999999998</v>
       </c>
       <c r="D47" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>201</v>
-      </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C48">
         <v>825.42269999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C49">
         <v>842.43799999999999</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C50">
         <v>855.43330000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4">
       <c r="B51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C51">
         <v>999.51189999999997</v>
       </c>
       <c r="D51" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="B52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C52">
         <v>1029.5225</v>
       </c>
       <c r="D52" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -6611,12 +6607,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4AB2D5-782B-41CE-B785-043075CF499C}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>77</v>
       </c>
@@ -6627,7 +6623,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="E2" t="s">
         <v>87</v>
       </c>
@@ -6653,7 +6649,7 @@
         <v>16.0001</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="B3" t="s">
         <v>79</v>
       </c>
@@ -6664,7 +6660,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -6679,7 +6675,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -6701,12 +6697,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f82b70a8-9591-478e-a6d5-bf315b83c485" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6866,17 +6861,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f82b70a8-9591-478e-a6d5-bf315b83c485" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E671EDC-6F53-464A-A6F7-50725C78A063}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D823E61-17DC-4359-821B-B50476FA651C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6900,17 +6904,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D823E61-17DC-4359-821B-B50476FA651C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E671EDC-6F53-464A-A6F7-50725C78A063}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>